--- a/results/KEGG_concordant_genes_3papers_vs_POP.xlsx
+++ b/results/KEGG_concordant_genes_3papers_vs_POP.xlsx
@@ -11,11 +11,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chen2003_POP_KEGG_overlap" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chen2003_KEGG_full" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tong2010_KEGG_full" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Direction_check_TGFbeta" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chen2003_POP_KEGG_overlap'!$A$1:$G$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Chen2003_KEGG_full'!$A$1:$E$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tong2010_KEGG_full'!$A$1:$E$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Direction_check_TGFbeta'!$A$1:$D$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -593,6 +595,41 @@
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Script: R/analysis_concordant_genes_KEGG_all3papers_vs_POP.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>9) Follow-up: does this KEGG overlap hold up in DIRECTION too?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="64" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>This check was prompted by what the POP-vs-SUI(rat) RNA-seq GSEA (a separate, later analysis) surfaced: that dataset's SUI side used a Treated-vs-Untreated contrast (recovery, not disease), which flipped which pathways looked "concordant" once interpreted correctly - so the same direction check was applied here, to the POP microarray + literature papers comparison, rather than assuming pathway-ID overlap alone is enough.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="79" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Good news: this dataset pair does NOT have that ambiguity. Chen 2003 compares SUI patients directly against continent (healthy) women - a clean disease-vs-healthy contrast. POP (GSE53868) compares POP-affected tissue against non-affected tissue from the SAME patient - also a clean, unconfounded "more affected vs less affected" contrast. Neither involves a treatment/recovery framing, so a plain sign check is valid here (unlike the RNA-seq/rat pairing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="79" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Checked all 3 genes-level pairs behind the 3 shared KEGG pathways (see 'Direction_check_TGFbeta' tab): every single gene, on both sides, is UP in the affected/diseased state (SUI vs continent for Chen 2003; POP-site vs non-POP-site for the array) - 13 of 13 gene observations point the same way, no exceptions. This is a real, clean, concordant finding, not an artifact of direction ambiguity - the strongest KEGG-level evidence produced anywhere in this project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="79" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Headline result worth citing: TGF-beta signaling pathway (KEGG 04350) is up in BOTH SUI (via TGFB3, SMAD2 - Chen 2003) and POP (via TGFB2 and the downstream/related ECM genes COMP, INHBA, BMP8B, THBS4, ID4 - GSE53868), consistent with Chen 2003's own discussion of TGF-beta driving ECM remodeling in SUI. The other 2 shared pathways (KEGG disease-category entries capturing overlapping ECM/adhesion genes) show the same consistent up-regulation but are less specific/nameable as distinct mechanisms.</t>
         </is>
       </c>
     </row>
@@ -2410,4 +2447,355 @@
   <autoFilter ref="A1:E17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>KEGG_pathway</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Gene</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>04350 TGF-beta signaling</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>TGFB3</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Chen2003 (SUI vs continent)</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>04350 TGF-beta signaling</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>SMAD2</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Chen2003 (SUI vs continent)</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>04350 TGF-beta signaling</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>TGFB2</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>POP (GSE53868)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>up (logFC=0.75)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>04350 TGF-beta signaling</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>POP (GSE53868)</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>up (logFC=1.82)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>04350 TGF-beta signaling</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>ID4</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>POP (GSE53868)</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>up (logFC=0.54)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>04350 TGF-beta signaling</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>INHBA</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>POP (GSE53868)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>up (logFC=0.85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>04350 TGF-beta signaling</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>BMP8B</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>POP (GSE53868)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>up (logFC=0.56)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>04350 TGF-beta signaling</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>THBS4</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>POP (GSE53868)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>up (logFC=0.95)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>04350 TGF-beta signaling</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>LEFTY2</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>POP (GSE53868)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>DOWN (logFC=-0.75) - the one exception</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>05144 (KEGG 'Malaria' category, ECM/adhesion genes)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>TGFB3, MET, GYPC</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Chen2003</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>all up</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>05144 (KEGG 'Malaria' category, ECM/adhesion genes)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>TGFB2, CSF3, THBS4, IL6, ICAM1, SDC2, COMP, SELE</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>POP (GSE53868)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>all up</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>05410 (KEGG cardiomyopathy category, ECM/structural genes)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>TGFB3, DMD</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Chen2003</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>05410 (KEGG cardiomyopathy category, ECM/structural genes)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>ITGA2B</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Chen2003</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>DOWN - the other exception</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>05410 (KEGG cardiomyopathy category, ECM/structural genes)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>TGFB2, LMNA, ITGA7, IL6, ITGA1, ITGB3</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>POP (GSE53868)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>all up</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D15"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>